--- a/branches/dev/ValueSet-mii-vs-consent-policy.xlsx
+++ b/branches/dev/ValueSet-mii-vs-consent-policy.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:08:36+00:00</t>
+    <t>2026-09-14T20:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-consent-policy.xlsx
+++ b/branches/dev/ValueSet-mii-vs-consent-policy.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:46:54+00:00</t>
+    <t>2026-10-06T12:38:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
